--- a/30_ETF_Construction_Management/_template_ETF.xlsx
+++ b/30_ETF_Construction_Management/_template_ETF.xlsx
@@ -2953,6 +2953,306 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 11]</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 11]</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 12]</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 12]</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 13]</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 13]</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 14]</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 14]</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 15]</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 15]</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 16]</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 16]</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 17]</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 17]</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 18]</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 18]</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 19]</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 19]</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 20]</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 20]</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 21]</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 21]</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 22]</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 22]</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 23]</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 23]</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 24]</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 24]</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 25]</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 25]</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 26]</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 26]</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 27]</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 27]</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 28]</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 28]</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 29]</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 29]</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>[Holding 30]</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>[Issuer 30]</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
@@ -3044,6 +3344,66 @@
       </c>
       <c r="C44" s="11" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 6]</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 7]</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 8]</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 9]</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 10]</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>[Sector 11]</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">

--- a/30_ETF_Construction_Management/_template_ETF.xlsx
+++ b/30_ETF_Construction_Management/_template_ETF.xlsx
@@ -2953,6 +2953,106 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="11" t="n"/>
+    </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
@@ -3045,6 +3145,30 @@
       <c r="C44" s="11" t="n">
         <v>0.08</v>
       </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
